--- a/GAC-App/Gateway 5S Checklist_2.xlsx
+++ b/GAC-App/Gateway 5S Checklist_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerry Hernandez\Documents\Operations Head\Special Projects\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\JR-files\GAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE103D43-9076-4576-8204-A65C0D642DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CCAD58-D6E2-4706-A938-76763DC34C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sales!$A$1:$E$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Service!$A$1:$E$49</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1761,21 +1761,33 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1788,12 +1800,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1848,6 +1854,42 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1863,50 +1905,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2682,35 +2682,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="39" customWidth="1"/>
-    <col min="2" max="2" width="83.59765625" style="39" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" style="39" customWidth="1"/>
-    <col min="4" max="4" width="25.09765625" style="39" customWidth="1"/>
-    <col min="5" max="5" width="25.8984375" style="39" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="39"/>
+    <col min="2" max="2" width="83.6640625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="39" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" style="39" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="53.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:5" ht="53.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-    </row>
-    <row r="2" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="135" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+    </row>
+    <row r="2" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-    </row>
-    <row r="3" spans="1:5" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+    </row>
+    <row r="3" spans="1:5" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
         <v>1</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="90" t="s">
         <v>7</v>
       </c>
@@ -2736,7 +2736,7 @@
       <c r="D4" s="91"/>
       <c r="E4" s="91"/>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46">
         <v>1</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="D5" s="48"/>
       <c r="E5" s="49"/>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46">
         <v>2</v>
       </c>
@@ -2758,16 +2758,16 @@
       <c r="D6" s="48"/>
       <c r="E6" s="49"/>
     </row>
-    <row r="7" spans="1:5" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="92" t="s">
+    <row r="7" spans="1:5" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="97"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="46">
         <v>3</v>
       </c>
@@ -2778,7 +2778,7 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46">
         <v>4</v>
       </c>
@@ -2789,7 +2789,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="46">
         <v>5</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46">
         <v>6</v>
       </c>
@@ -2811,7 +2811,7 @@
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="46">
         <v>7</v>
       </c>
@@ -2822,7 +2822,7 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="46">
         <v>8</v>
       </c>
@@ -2833,7 +2833,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="46">
         <v>9</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46">
         <v>10</v>
       </c>
@@ -2855,7 +2855,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="46">
         <v>11</v>
       </c>
@@ -2866,16 +2866,16 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="94" t="s">
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="99"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="46">
         <v>12</v>
       </c>
@@ -2886,7 +2886,7 @@
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="46">
         <v>13</v>
       </c>
@@ -2897,18 +2897,18 @@
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="94" t="s">
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="46">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B21" s="44" t="s">
         <v>177</v>
@@ -2917,9 +2917,9 @@
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="80">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B22" s="81" t="s">
         <v>178</v>
@@ -2928,8 +2928,10 @@
       <c r="D22" s="82"/>
       <c r="E22" s="82"/>
     </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="83">
+        <v>16</v>
+      </c>
       <c r="B23" s="84" t="s">
         <v>179</v>
       </c>
@@ -2937,18 +2939,18 @@
       <c r="D23" s="85"/>
       <c r="E23" s="85"/>
     </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="96" t="s">
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="97"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="97"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="46">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>32</v>
@@ -2957,9 +2959,9 @@
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="46">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B26" s="43" t="s">
         <v>33</v>
@@ -2968,9 +2970,9 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="46">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B27" s="43" t="s">
         <v>36</v>
@@ -2979,9 +2981,9 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="46">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B28" s="43" t="s">
         <v>34</v>
@@ -2990,9 +2992,9 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="46">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B29" s="44" t="s">
         <v>10</v>
@@ -3001,9 +3003,9 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="46">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B30" s="44" t="s">
         <v>11</v>
@@ -3012,9 +3014,9 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="46">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B31" s="44" t="s">
         <v>12</v>
@@ -3023,9 +3025,9 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="46">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B32" s="43" t="s">
         <v>35</v>
@@ -3034,9 +3036,9 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="46">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B33" s="44" t="s">
         <v>13</v>
@@ -3045,9 +3047,9 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="46">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" s="43" t="s">
         <v>38</v>
@@ -3056,9 +3058,9 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="46">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B35" s="43" t="s">
         <v>37</v>
@@ -3067,7 +3069,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="90" t="s">
         <v>14</v>
       </c>
@@ -3076,9 +3078,9 @@
       <c r="D36" s="91"/>
       <c r="E36" s="91"/>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="46">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B37" s="43" t="s">
         <v>39</v>
@@ -3087,9 +3089,9 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="46">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B38" s="43" t="s">
         <v>40</v>
@@ -3098,9 +3100,9 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="46">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B39" s="43" t="s">
         <v>41</v>
@@ -3109,9 +3111,9 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="46">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B40" s="43" t="s">
         <v>42</v>
@@ -3120,9 +3122,9 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="46">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B41" s="43" t="s">
         <v>43</v>
@@ -3131,9 +3133,9 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="46">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B42" s="43" t="s">
         <v>44</v>
@@ -3142,9 +3144,9 @@
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
     </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="46">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B43" s="43" t="s">
         <v>45</v>
@@ -3153,9 +3155,9 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="46">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B44" s="44" t="s">
         <v>15</v>
@@ -3164,7 +3166,7 @@
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
     </row>
-    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="90" t="s">
         <v>16</v>
       </c>
@@ -3173,9 +3175,9 @@
       <c r="D45" s="91"/>
       <c r="E45" s="91"/>
     </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="46">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B46" s="43" t="s">
         <v>47</v>
@@ -3184,9 +3186,9 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="46">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B47" s="43" t="s">
         <v>96</v>
@@ -3195,9 +3197,9 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
     </row>
-    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="46">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B48" s="43" t="s">
         <v>46</v>
@@ -3206,9 +3208,9 @@
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
     </row>
-    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="46">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B49" s="43" t="s">
         <v>49</v>
@@ -3217,9 +3219,9 @@
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
     </row>
-    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="46">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B50" s="43" t="s">
         <v>27</v>
@@ -3228,9 +3230,9 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
     </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="46">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B51" s="43" t="s">
         <v>48</v>
@@ -3239,7 +3241,7 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
     </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="90" t="s">
         <v>17</v>
       </c>
@@ -3248,9 +3250,9 @@
       <c r="D52" s="91"/>
       <c r="E52" s="91"/>
     </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="46">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B53" s="43" t="s">
         <v>50</v>
@@ -3259,9 +3261,9 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
     </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="46">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B54" s="43" t="s">
         <v>51</v>
@@ -3270,19 +3272,19 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
     </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="46">
-        <v>40</v>
-      </c>
-      <c r="B55" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="44" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
     </row>
-    <row r="56" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="59"/>
       <c r="B57" s="60" t="s">
         <v>115</v>
@@ -3291,14 +3293,14 @@
       <c r="D57" s="76"/>
       <c r="E57" s="53"/>
     </row>
-    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="61"/>
       <c r="B58" s="54"/>
       <c r="C58" s="58"/>
       <c r="D58" s="54"/>
       <c r="E58" s="55"/>
     </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="62"/>
       <c r="B59" s="63" t="s">
         <v>114</v>
@@ -3332,35 +3334,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E47"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="45" customWidth="1"/>
-    <col min="2" max="2" width="83.59765625" style="39" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" style="39" customWidth="1"/>
-    <col min="4" max="4" width="25.09765625" style="39" customWidth="1"/>
-    <col min="5" max="5" width="22.69921875" style="39" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="39"/>
+    <col min="2" max="2" width="83.6640625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="39" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="39" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="39"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="47.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="98" t="s">
+    <row r="2" spans="1:5" ht="47.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-    </row>
-    <row r="3" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="135" t="s">
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+    </row>
+    <row r="3" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-    </row>
-    <row r="4" spans="1:5" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+    </row>
+    <row r="4" spans="1:5" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
@@ -3377,7 +3379,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="90" t="s">
         <v>7</v>
       </c>
@@ -3386,18 +3388,18 @@
       <c r="D5" s="91"/>
       <c r="E5" s="91"/>
     </row>
-    <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="41">
         <v>1</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="134"/>
+      <c r="C6" s="87"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="41">
         <v>2</v>
       </c>
@@ -3408,16 +3410,16 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="92" t="s">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="41">
         <v>3</v>
       </c>
@@ -3428,7 +3430,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="41">
         <v>4</v>
       </c>
@@ -3439,7 +3441,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="41">
         <v>5</v>
       </c>
@@ -3450,9 +3452,9 @@
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="43" t="s">
         <v>24</v>
@@ -3461,9 +3463,9 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>8</v>
@@ -3472,9 +3474,9 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="43" t="s">
         <v>62</v>
@@ -3483,9 +3485,9 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>26</v>
@@ -3494,9 +3496,9 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="41">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="43" t="s">
         <v>27</v>
@@ -3505,9 +3507,9 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="41">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="43" t="s">
         <v>31</v>
@@ -3516,18 +3518,18 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92" t="s">
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="97"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="41">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="43" t="s">
         <v>117</v>
@@ -3536,9 +3538,9 @@
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="1:5" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="41">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="43" t="s">
         <v>63</v>
@@ -3547,9 +3549,9 @@
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" s="43" t="s">
         <v>64</v>
@@ -3558,9 +3560,9 @@
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="41">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B22" s="43" t="s">
         <v>65</v>
@@ -3569,9 +3571,9 @@
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="41">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B23" s="43" t="s">
         <v>66</v>
@@ -3580,9 +3582,9 @@
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="41">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="43" t="s">
         <v>67</v>
@@ -3591,18 +3593,18 @@
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="96" t="s">
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="97"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="41">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B26" s="43" t="s">
         <v>39</v>
@@ -3611,9 +3613,9 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B27" s="43" t="s">
         <v>40</v>
@@ -3622,9 +3624,9 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="41">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B28" s="43" t="s">
         <v>41</v>
@@ -3633,9 +3635,9 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="41">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B29" s="43" t="s">
         <v>42</v>
@@ -3644,9 +3646,9 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="41">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B30" s="43" t="s">
         <v>43</v>
@@ -3655,9 +3657,9 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="41">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B31" s="43" t="s">
         <v>44</v>
@@ -3666,9 +3668,9 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="41">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B32" s="43" t="s">
         <v>45</v>
@@ -3677,9 +3679,9 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="41">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B33" s="44" t="s">
         <v>15</v>
@@ -3688,7 +3690,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="90" t="s">
         <v>16</v>
       </c>
@@ -3697,9 +3699,9 @@
       <c r="D34" s="91"/>
       <c r="E34" s="91"/>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="41">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B35" s="43" t="s">
         <v>47</v>
@@ -3708,9 +3710,9 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="41">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B36" s="43" t="s">
         <v>96</v>
@@ -3719,9 +3721,9 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="41">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B37" s="43" t="s">
         <v>46</v>
@@ -3730,9 +3732,9 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="41">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B38" s="43" t="s">
         <v>49</v>
@@ -3741,9 +3743,9 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="41">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B39" s="43" t="s">
         <v>27</v>
@@ -3752,9 +3754,9 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="41">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B40" s="43" t="s">
         <v>48</v>
@@ -3763,18 +3765,18 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="94" t="s">
+    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="95"/>
-      <c r="C41" s="95"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="95"/>
-    </row>
-    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="99"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="99"/>
+    </row>
+    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="41">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B42" s="43" t="s">
         <v>50</v>
@@ -3783,9 +3785,9 @@
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
     </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="41">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B43" s="43" t="s">
         <v>51</v>
@@ -3794,8 +3796,8 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="59"/>
       <c r="B45" s="60" t="s">
         <v>115</v>
@@ -3804,14 +3806,14 @@
       <c r="D45" s="76"/>
       <c r="E45" s="53"/>
     </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="61"/>
       <c r="B46" s="54"/>
       <c r="C46" s="58"/>
       <c r="D46" s="54"/>
       <c r="E46" s="55"/>
     </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="62"/>
       <c r="B47" s="63" t="s">
         <v>116</v>
@@ -3843,37 +3845,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F74"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="83.59765625" customWidth="1"/>
-    <col min="3" max="3" width="6.8984375" customWidth="1"/>
-    <col min="4" max="4" width="7.09765625" customWidth="1"/>
-    <col min="5" max="5" width="6.8984375" customWidth="1"/>
-    <col min="6" max="6" width="25.09765625" customWidth="1"/>
+    <col min="2" max="2" width="83.6640625" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+    <row r="2" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="108"/>
-    </row>
-    <row r="3" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="109" t="s">
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+    </row>
+    <row r="3" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="111"/>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="113"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3893,17 +3895,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="112" t="s">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="114"/>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="115"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="116"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>1</v>
       </c>
@@ -3915,7 +3917,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>2</v>
       </c>
@@ -3927,17 +3929,17 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="115" t="s">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="113"/>
-      <c r="D8" s="113"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="114"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="115"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="116"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>3</v>
       </c>
@@ -3949,7 +3951,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>4</v>
       </c>
@@ -3961,7 +3963,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -3973,7 +3975,7 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -3985,7 +3987,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>7</v>
       </c>
@@ -3997,7 +3999,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>8</v>
       </c>
@@ -4009,7 +4011,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>9</v>
       </c>
@@ -4021,7 +4023,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>10</v>
       </c>
@@ -4033,7 +4035,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>11</v>
       </c>
@@ -4045,17 +4047,17 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="115" t="s">
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="113"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="114"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="116"/>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>12</v>
       </c>
@@ -4067,7 +4069,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>13</v>
       </c>
@@ -4079,17 +4081,17 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="112" t="s">
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="114" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="113"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="114"/>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="115"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>14</v>
       </c>
@@ -4101,7 +4103,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>15</v>
       </c>
@@ -4113,7 +4115,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>16</v>
       </c>
@@ -4125,7 +4127,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>17</v>
       </c>
@@ -4137,7 +4139,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>18</v>
       </c>
@@ -4149,7 +4151,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>19</v>
       </c>
@@ -4161,7 +4163,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>20</v>
       </c>
@@ -4173,7 +4175,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>21</v>
       </c>
@@ -4185,7 +4187,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>22</v>
       </c>
@@ -4197,7 +4199,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>23</v>
       </c>
@@ -4209,7 +4211,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>24</v>
       </c>
@@ -4221,17 +4223,17 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="115" t="s">
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="113"/>
-      <c r="C33" s="113"/>
-      <c r="D33" s="113"/>
-      <c r="E33" s="113"/>
-      <c r="F33" s="114"/>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="115"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
+      <c r="F33" s="116"/>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>25</v>
       </c>
@@ -4243,7 +4245,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>26</v>
       </c>
@@ -4255,7 +4257,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>27</v>
       </c>
@@ -4267,7 +4269,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>28</v>
       </c>
@@ -4279,7 +4281,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>29</v>
       </c>
@@ -4291,7 +4293,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>30</v>
       </c>
@@ -4303,7 +4305,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>31</v>
       </c>
@@ -4315,7 +4317,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>32</v>
       </c>
@@ -4327,17 +4329,17 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="115" t="s">
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="113"/>
-      <c r="C42" s="113"/>
-      <c r="D42" s="113"/>
-      <c r="E42" s="113"/>
-      <c r="F42" s="114"/>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="115"/>
+      <c r="C42" s="115"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="115"/>
+      <c r="F42" s="116"/>
+    </row>
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>33</v>
       </c>
@@ -4349,7 +4351,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>34</v>
       </c>
@@ -4361,7 +4363,7 @@
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>35</v>
       </c>
@@ -4373,7 +4375,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>36</v>
       </c>
@@ -4385,7 +4387,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>37</v>
       </c>
@@ -4397,7 +4399,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>38</v>
       </c>
@@ -4409,7 +4411,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>39</v>
       </c>
@@ -4421,17 +4423,17 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="112" t="s">
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="114" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="114"/>
+      <c r="B50" s="116"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>40</v>
       </c>
@@ -4443,7 +4445,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>41</v>
       </c>
@@ -4455,7 +4457,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>42</v>
       </c>
@@ -4467,7 +4469,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>43</v>
       </c>
@@ -4479,7 +4481,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>44</v>
       </c>
@@ -4491,7 +4493,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>45</v>
       </c>
@@ -4503,7 +4505,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>46</v>
       </c>
@@ -4515,7 +4517,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>47</v>
       </c>
@@ -4527,17 +4529,17 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="112" t="s">
+    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="B59" s="114"/>
+      <c r="B59" s="116"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>48</v>
       </c>
@@ -4549,7 +4551,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>49</v>
       </c>
@@ -4561,7 +4563,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>50</v>
       </c>
@@ -4573,7 +4575,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>51</v>
       </c>
@@ -4585,7 +4587,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>52</v>
       </c>
@@ -4597,7 +4599,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>53</v>
       </c>
@@ -4609,17 +4611,17 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="112" t="s">
+    <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="113"/>
-      <c r="C66" s="113"/>
-      <c r="D66" s="113"/>
-      <c r="E66" s="113"/>
-      <c r="F66" s="114"/>
-    </row>
-    <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="115"/>
+      <c r="C66" s="115"/>
+      <c r="D66" s="115"/>
+      <c r="E66" s="115"/>
+      <c r="F66" s="116"/>
+    </row>
+    <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>54</v>
       </c>
@@ -4631,7 +4633,7 @@
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>39</v>
       </c>
@@ -4643,7 +4645,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>40</v>
       </c>
@@ -4655,39 +4657,39 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:6" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:6" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B71" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C71" s="100" t="s">
+      <c r="C71" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="100"/>
-      <c r="E71" s="100"/>
-      <c r="F71" s="101"/>
-    </row>
-    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="102"/>
+      <c r="E71" s="102"/>
+      <c r="F71" s="103"/>
+    </row>
+    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C72" s="102"/>
-      <c r="D72" s="102"/>
-      <c r="E72" s="102"/>
-      <c r="F72" s="103"/>
-    </row>
-    <row r="73" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C72" s="104"/>
+      <c r="D72" s="104"/>
+      <c r="E72" s="104"/>
+      <c r="F72" s="105"/>
+    </row>
+    <row r="73" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B73" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="104" t="s">
+      <c r="C73" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="D73" s="104"/>
-      <c r="E73" s="104"/>
-      <c r="F73" s="105"/>
-    </row>
-    <row r="74" spans="1:6" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D73" s="106"/>
+      <c r="E73" s="106"/>
+      <c r="F73" s="107"/>
+    </row>
+    <row r="74" spans="1:6" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="C71:F71"/>
@@ -4706,7 +4708,7 @@
     <mergeCell ref="A66:F66"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="59" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup scale="57" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4714,47 +4716,47 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="20.796875" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="15"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
     </row>
-    <row r="3" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="130"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-    </row>
-    <row r="4" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="130"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-    </row>
-    <row r="5" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="119" t="s">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+    </row>
+    <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="118"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+    </row>
+    <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="133" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
@@ -4768,12 +4770,12 @@
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
     </row>
-    <row r="6" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="119"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
+    <row r="6" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="133"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -4787,7 +4789,7 @@
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
     </row>
-    <row r="7" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>73</v>
       </c>
@@ -4795,39 +4797,39 @@
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="123" t="s">
+      <c r="F7" s="135" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123" t="s">
+      <c r="G7" s="135"/>
+      <c r="H7" s="135" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123" t="s">
+      <c r="I7" s="135"/>
+      <c r="J7" s="135" t="s">
         <v>94</v>
       </c>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123" t="s">
+      <c r="K7" s="135"/>
+      <c r="L7" s="135" t="s">
         <v>76</v>
       </c>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123" t="s">
+      <c r="M7" s="135"/>
+      <c r="N7" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="123"/>
-      <c r="P7" s="123" t="s">
+      <c r="O7" s="135"/>
+      <c r="P7" s="135" t="s">
         <v>78</v>
       </c>
-      <c r="Q7" s="123"/>
-    </row>
-    <row r="8" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="131" t="s">
+      <c r="Q7" s="135"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="125" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="133"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="127"/>
       <c r="F8" s="18" t="s">
         <v>92</v>
       </c>
@@ -4865,14 +4867,14 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="128" t="s">
+    <row r="9" spans="1:17" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="129"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="129"/>
-      <c r="E9" s="129"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
@@ -4886,14 +4888,14 @@
       <c r="P9" s="18"/>
       <c r="Q9" s="18"/>
     </row>
-    <row r="10" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="121" t="s">
+    <row r="10" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -4907,14 +4909,14 @@
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
     </row>
-    <row r="11" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="124" t="s">
+    <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="121" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
@@ -4928,14 +4930,14 @@
       <c r="P11" s="18"/>
       <c r="Q11" s="18"/>
     </row>
-    <row r="12" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="128" t="s">
+    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
@@ -4949,14 +4951,14 @@
       <c r="P12" s="18"/>
       <c r="Q12" s="18"/>
     </row>
-    <row r="13" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="121" t="s">
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
@@ -4970,14 +4972,14 @@
       <c r="P13" s="18"/>
       <c r="Q13" s="18"/>
     </row>
-    <row r="14" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="124" t="s">
+    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="121" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
@@ -4991,14 +4993,14 @@
       <c r="P14" s="18"/>
       <c r="Q14" s="18"/>
     </row>
-    <row r="15" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="128" t="s">
+    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
@@ -5012,14 +5014,14 @@
       <c r="P15" s="18"/>
       <c r="Q15" s="18"/>
     </row>
-    <row r="16" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="121" t="s">
+    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="119" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
@@ -5033,14 +5035,14 @@
       <c r="P16" s="18"/>
       <c r="Q16" s="18"/>
     </row>
-    <row r="17" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="124" t="s">
+    <row r="17" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="125"/>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
@@ -5054,88 +5056,71 @@
       <c r="P17" s="18"/>
       <c r="Q17" s="18"/>
     </row>
-    <row r="18" spans="1:17" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="126" t="s">
+    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="128" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="127"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="116"/>
-      <c r="O18" s="116"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="116"/>
-    </row>
-    <row r="19" spans="1:17" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="120" t="s">
+      <c r="B18" s="129"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
+      <c r="M18" s="130"/>
+      <c r="N18" s="130"/>
+      <c r="O18" s="130"/>
+      <c r="P18" s="130"/>
+      <c r="Q18" s="130"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="134" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="117"/>
-      <c r="N19" s="117"/>
-      <c r="O19" s="117"/>
-      <c r="P19" s="117"/>
-      <c r="Q19" s="117"/>
-    </row>
-    <row r="20" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="121" t="s">
+      <c r="B19" s="133"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="131"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="131"/>
+      <c r="N19" s="131"/>
+      <c r="O19" s="131"/>
+      <c r="P19" s="131"/>
+      <c r="Q19" s="131"/>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="118"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="118"/>
-      <c r="Q20" s="118"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="132"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="132"/>
+      <c r="M20" s="132"/>
+      <c r="N20" s="132"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A3:E4"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="P18:P20"/>
     <mergeCell ref="Q18:Q20"/>
     <mergeCell ref="A5:E6"/>
     <mergeCell ref="G18:G20"/>
@@ -5152,6 +5137,23 @@
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="P18:P20"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A3:E4"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -5162,35 +5164,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="161.09765625" style="19" customWidth="1"/>
+    <col min="1" max="1" width="161.1640625" style="19" customWidth="1"/>
     <col min="2" max="2" width="1" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="19" customWidth="1"/>
     <col min="4" max="4" width="1" style="19" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="19" customWidth="1"/>
     <col min="6" max="6" width="1" style="19" customWidth="1"/>
-    <col min="7" max="7" width="10.69921875" style="19" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="19" customWidth="1"/>
     <col min="8" max="8" width="1" style="19" customWidth="1"/>
-    <col min="9" max="9" width="10.69921875" style="19" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="19" customWidth="1"/>
     <col min="10" max="10" width="1" style="19" customWidth="1"/>
-    <col min="11" max="11" width="10.69921875" style="19" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" style="19" customWidth="1"/>
     <col min="12" max="12" width="1" style="19" customWidth="1"/>
-    <col min="13" max="13" width="10.69921875" style="19" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" style="19" customWidth="1"/>
     <col min="14" max="14" width="1" style="19" customWidth="1"/>
-    <col min="15" max="15" width="10.69921875" style="19" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" style="19" customWidth="1"/>
     <col min="16" max="16" width="1" style="19" customWidth="1"/>
-    <col min="17" max="17" width="10.69921875" style="19" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" style="19" customWidth="1"/>
     <col min="18" max="18" width="1" style="19" customWidth="1"/>
-    <col min="19" max="19" width="10.69921875" style="19" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" style="19" customWidth="1"/>
     <col min="20" max="20" width="1" style="19" customWidth="1"/>
-    <col min="21" max="21" width="62.3984375" style="19" customWidth="1"/>
-    <col min="22" max="23" width="9.09765625" style="19" customWidth="1"/>
-    <col min="24" max="16384" width="9.09765625" style="19"/>
+    <col min="21" max="21" width="62.33203125" style="19" customWidth="1"/>
+    <col min="22" max="23" width="9.1640625" style="19" customWidth="1"/>
+    <col min="24" max="16384" width="9.1640625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="95.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:21" s="21" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="95.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:21" s="21" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>97</v>
       </c>
@@ -5198,10 +5200,10 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="22" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:21" s="22" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="21"/>
     </row>
-    <row r="4" spans="1:21" s="25" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" s="25" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
         <v>99</v>
       </c>
@@ -5246,7 +5248,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="26" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="26" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="27"/>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
@@ -5268,10 +5270,10 @@
       <c r="T5" s="27"/>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="28"/>
     </row>
-    <row r="7" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="34" t="s">
         <v>113</v>
       </c>
@@ -5286,10 +5288,10 @@
       <c r="S7" s="29"/>
       <c r="U7" s="30"/>
     </row>
-    <row r="8" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35"/>
     </row>
-    <row r="9" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="36" t="s">
         <v>101</v>
       </c>
@@ -5304,10 +5306,10 @@
       <c r="S9" s="29"/>
       <c r="U9" s="30"/>
     </row>
-    <row r="10" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35"/>
     </row>
-    <row r="11" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="36" t="s">
         <v>107</v>
       </c>
@@ -5322,10 +5324,10 @@
       <c r="S11" s="29"/>
       <c r="U11" s="30"/>
     </row>
-    <row r="12" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35"/>
     </row>
-    <row r="13" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="36" t="s">
         <v>108</v>
       </c>
@@ -5340,10 +5342,10 @@
       <c r="S13" s="29"/>
       <c r="U13" s="30"/>
     </row>
-    <row r="14" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35"/>
     </row>
-    <row r="15" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="36" t="s">
         <v>109</v>
       </c>
@@ -5358,10 +5360,10 @@
       <c r="S15" s="29"/>
       <c r="U15" s="30"/>
     </row>
-    <row r="16" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35"/>
     </row>
-    <row r="17" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="37" t="s">
         <v>110</v>
       </c>
@@ -5376,10 +5378,10 @@
       <c r="S17" s="29"/>
       <c r="U17" s="30"/>
     </row>
-    <row r="18" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35"/>
     </row>
-    <row r="19" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="36" t="s">
         <v>111</v>
       </c>
@@ -5394,10 +5396,10 @@
       <c r="S19" s="29"/>
       <c r="U19" s="30"/>
     </row>
-    <row r="20" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35"/>
     </row>
-    <row r="21" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="36" t="s">
         <v>102</v>
       </c>
@@ -5412,10 +5414,10 @@
       <c r="S21" s="29"/>
       <c r="U21" s="30"/>
     </row>
-    <row r="22" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35"/>
     </row>
-    <row r="23" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="36" t="s">
         <v>112</v>
       </c>
@@ -5430,10 +5432,10 @@
       <c r="S23" s="29"/>
       <c r="U23" s="30"/>
     </row>
-    <row r="24" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35"/>
     </row>
-    <row r="25" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36" t="s">
         <v>103</v>
       </c>
@@ -5448,10 +5450,10 @@
       <c r="S25" s="29"/>
       <c r="U25" s="30"/>
     </row>
-    <row r="26" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35"/>
     </row>
-    <row r="27" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
         <v>104</v>
       </c>
@@ -5466,20 +5468,20 @@
       <c r="S27" s="29"/>
       <c r="U27" s="30"/>
     </row>
-    <row r="28" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="31"/>
     </row>
-    <row r="29" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="31" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="32" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C37" s="33"/>
       <c r="E37" s="33"/>
       <c r="G37" s="33"/>
@@ -5500,17 +5502,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893F2515-F132-4075-859E-E883026B1714}">
   <dimension ref="B3:M43"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="65"/>
+    <col min="1" max="1" width="8.83203125" style="65"/>
     <col min="2" max="2" width="34" style="65" customWidth="1"/>
-    <col min="3" max="11" width="8.796875" style="65"/>
+    <col min="3" max="11" width="8.83203125" style="65"/>
     <col min="12" max="12" width="22" style="64" customWidth="1"/>
-    <col min="13" max="13" width="22.69921875" style="65" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="65"/>
+    <col min="13" max="13" width="22.6640625" style="65" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="65"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" ht="21.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="66" t="s">
         <v>146</v>
       </c>
@@ -5548,7 +5550,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="70" t="s">
         <v>118</v>
       </c>
@@ -5564,7 +5566,7 @@
       <c r="L4" s="75"/>
       <c r="M4" s="75"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" s="73" t="s">
         <v>131</v>
       </c>
@@ -5580,7 +5582,7 @@
       <c r="L5" s="72"/>
       <c r="M5" s="72"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6" s="73" t="s">
         <v>132</v>
       </c>
@@ -5596,7 +5598,7 @@
       <c r="L6" s="72"/>
       <c r="M6" s="72"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B7" s="70" t="s">
         <v>128</v>
       </c>
@@ -5612,7 +5614,7 @@
       <c r="L7" s="75"/>
       <c r="M7" s="75"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" s="73" t="s">
         <v>155</v>
       </c>
@@ -5628,7 +5630,7 @@
       <c r="L8" s="72"/>
       <c r="M8" s="72"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B9" s="73" t="s">
         <v>156</v>
       </c>
@@ -5644,7 +5646,7 @@
       <c r="L9" s="72"/>
       <c r="M9" s="72"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10" s="73" t="s">
         <v>157</v>
       </c>
@@ -5660,7 +5662,7 @@
       <c r="L10" s="72"/>
       <c r="M10" s="72"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" s="70" t="s">
         <v>148</v>
       </c>
@@ -5676,7 +5678,7 @@
       <c r="L11" s="75"/>
       <c r="M11" s="75"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" s="73" t="s">
         <v>133</v>
       </c>
@@ -5692,7 +5694,7 @@
       <c r="L12" s="72"/>
       <c r="M12" s="72"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B13" s="73" t="s">
         <v>134</v>
       </c>
@@ -5708,7 +5710,7 @@
       <c r="L13" s="72"/>
       <c r="M13" s="72"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" s="73" t="s">
         <v>140</v>
       </c>
@@ -5724,7 +5726,7 @@
       <c r="L14" s="72"/>
       <c r="M14" s="72"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" s="70" t="s">
         <v>129</v>
       </c>
@@ -5740,7 +5742,7 @@
       <c r="L15" s="75"/>
       <c r="M15" s="75"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="73" t="s">
         <v>133</v>
       </c>
@@ -5756,7 +5758,7 @@
       <c r="L16" s="72"/>
       <c r="M16" s="72"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" s="73" t="s">
         <v>135</v>
       </c>
@@ -5772,7 +5774,7 @@
       <c r="L17" s="72"/>
       <c r="M17" s="72"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" s="73" t="s">
         <v>136</v>
       </c>
@@ -5788,7 +5790,7 @@
       <c r="L18" s="72"/>
       <c r="M18" s="72"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" s="73" t="s">
         <v>137</v>
       </c>
@@ -5804,7 +5806,7 @@
       <c r="L19" s="72"/>
       <c r="M19" s="72"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" s="70" t="s">
         <v>130</v>
       </c>
@@ -5820,7 +5822,7 @@
       <c r="L20" s="75"/>
       <c r="M20" s="75"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21" s="73" t="s">
         <v>133</v>
       </c>
@@ -5836,7 +5838,7 @@
       <c r="L21" s="72"/>
       <c r="M21" s="72"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22" s="73" t="s">
         <v>135</v>
       </c>
@@ -5852,7 +5854,7 @@
       <c r="L22" s="72"/>
       <c r="M22" s="72"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23" s="73" t="s">
         <v>137</v>
       </c>
@@ -5868,7 +5870,7 @@
       <c r="L23" s="72"/>
       <c r="M23" s="72"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24" s="70" t="s">
         <v>138</v>
       </c>
@@ -5884,7 +5886,7 @@
       <c r="L24" s="75"/>
       <c r="M24" s="75"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B25" s="73" t="s">
         <v>133</v>
       </c>
@@ -5900,7 +5902,7 @@
       <c r="L25" s="72"/>
       <c r="M25" s="72"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B26" s="73" t="s">
         <v>158</v>
       </c>
@@ -5916,7 +5918,7 @@
       <c r="L26" s="72"/>
       <c r="M26" s="72"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B27" s="73" t="s">
         <v>139</v>
       </c>
@@ -5932,7 +5934,7 @@
       <c r="L27" s="72"/>
       <c r="M27" s="72"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B28" s="73" t="s">
         <v>137</v>
       </c>
@@ -5948,7 +5950,7 @@
       <c r="L28" s="72"/>
       <c r="M28" s="72"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B29" s="70" t="s">
         <v>150</v>
       </c>
@@ -5964,7 +5966,7 @@
       <c r="L29" s="75"/>
       <c r="M29" s="75"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B30" s="73" t="s">
         <v>144</v>
       </c>
@@ -5980,7 +5982,7 @@
       <c r="L30" s="72"/>
       <c r="M30" s="72"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B31" s="73" t="s">
         <v>143</v>
       </c>
@@ -5996,7 +5998,7 @@
       <c r="L31" s="72"/>
       <c r="M31" s="72"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32" s="73" t="s">
         <v>142</v>
       </c>
@@ -6012,7 +6014,7 @@
       <c r="L32" s="72"/>
       <c r="M32" s="72"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B33" s="73" t="s">
         <v>145</v>
       </c>
@@ -6028,7 +6030,7 @@
       <c r="L33" s="72"/>
       <c r="M33" s="72"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B34" s="73" t="s">
         <v>141</v>
       </c>
@@ -6044,7 +6046,7 @@
       <c r="L34" s="72"/>
       <c r="M34" s="72"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35" s="73" t="s">
         <v>151</v>
       </c>
@@ -6060,7 +6062,7 @@
       <c r="L35" s="72"/>
       <c r="M35" s="72"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" s="73" t="s">
         <v>152</v>
       </c>
@@ -6076,7 +6078,7 @@
       <c r="L36" s="72"/>
       <c r="M36" s="72"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="70" t="s">
         <v>147</v>
       </c>
@@ -6092,7 +6094,7 @@
       <c r="L37" s="75"/>
       <c r="M37" s="75"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B38" s="73" t="s">
         <v>133</v>
       </c>
@@ -6108,7 +6110,7 @@
       <c r="L38" s="72"/>
       <c r="M38" s="72"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39" s="73" t="s">
         <v>149</v>
       </c>
@@ -6124,7 +6126,7 @@
       <c r="L39" s="72"/>
       <c r="M39" s="72"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40" s="70" t="s">
         <v>153</v>
       </c>
@@ -6140,7 +6142,7 @@
       <c r="L40" s="75"/>
       <c r="M40" s="75"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B41" s="73" t="s">
         <v>154</v>
       </c>
@@ -6156,7 +6158,7 @@
       <c r="L41" s="72"/>
       <c r="M41" s="72"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B42" s="70" t="s">
         <v>159</v>
       </c>
@@ -6172,7 +6174,7 @@
       <c r="L42" s="75"/>
       <c r="M42" s="75"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B43" s="73" t="s">
         <v>160</v>
       </c>
@@ -6197,18 +6199,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4EAFEC7-8ACA-4B9C-9FFD-0485A9914B7C}">
   <dimension ref="B2:G13"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="41.69921875" customWidth="1"/>
-    <col min="3" max="7" width="8.796875" style="77"/>
+    <col min="2" max="2" width="41.6640625" customWidth="1"/>
+    <col min="3" max="7" width="8.83203125" style="77"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C3" s="79" t="s">
         <v>168</v>
       </c>
@@ -6225,7 +6227,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>175</v>
       </c>
@@ -6243,7 +6245,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>28</v>
       </c>
@@ -6261,7 +6263,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>29</v>
       </c>
@@ -6276,7 +6278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>172</v>
       </c>
@@ -6294,7 +6296,7 @@
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="86" t="s">
         <v>176</v>
       </c>
@@ -6312,7 +6314,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>173</v>
       </c>
@@ -6333,7 +6335,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>174</v>
       </c>
@@ -6351,10 +6353,10 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="G11" s="78"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="G13" t="s">
         <v>163</v>
       </c>
